--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/140.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/140.xlsx
@@ -426,13 +426,13 @@
         <v>-12.16586419573545</v>
       </c>
       <c r="E2">
-        <v>-11.2563076487756</v>
+        <v>-16.24112051067291</v>
       </c>
       <c r="F2">
-        <v>-4.568506016139783</v>
+        <v>-4.789655261665167</v>
       </c>
       <c r="G2">
-        <v>-13.16036169869649</v>
+        <v>-13.63771709238607</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.90102400148324</v>
       </c>
       <c r="E3">
-        <v>-11.78551417825997</v>
+        <v>-16.34808759520809</v>
       </c>
       <c r="F3">
-        <v>-4.690180762099988</v>
+        <v>-4.840788724705175</v>
       </c>
       <c r="G3">
-        <v>-13.03234812077632</v>
+        <v>-14.00880028220835</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.64174711348054</v>
       </c>
       <c r="E4">
-        <v>-11.91455304510854</v>
+        <v>-15.54354078910935</v>
       </c>
       <c r="F4">
-        <v>-4.552507756489516</v>
+        <v>-5.051144342972081</v>
       </c>
       <c r="G4">
-        <v>-12.91911316475988</v>
+        <v>-15.03277765670738</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.41652661222725</v>
       </c>
       <c r="E5">
-        <v>-12.4037233358911</v>
+        <v>-17.09802100477433</v>
       </c>
       <c r="F5">
-        <v>-4.702658460288357</v>
+        <v>-5.117494086834113</v>
       </c>
       <c r="G5">
-        <v>-12.34116536172241</v>
+        <v>-14.02409897772926</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.20730293121915</v>
       </c>
       <c r="E6">
-        <v>-13.24050834845045</v>
+        <v>-18.27434194148079</v>
       </c>
       <c r="F6">
-        <v>-4.5501949547009</v>
+        <v>-5.066962018528538</v>
       </c>
       <c r="G6">
-        <v>-12.82066995553342</v>
+        <v>-13.32233263853536</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.01136228096383</v>
       </c>
       <c r="E7">
-        <v>-13.11893240676653</v>
+        <v>-17.86235043321096</v>
       </c>
       <c r="F7">
-        <v>-4.522384175886712</v>
+        <v>-5.489783106837281</v>
       </c>
       <c r="G7">
-        <v>-12.56120407949877</v>
+        <v>-13.0598742884385</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.81008711526884</v>
       </c>
       <c r="E8">
-        <v>-14.28544466877237</v>
+        <v>-19.50397207420555</v>
       </c>
       <c r="F8">
-        <v>-4.392853193478356</v>
+        <v>-5.112768250801142</v>
       </c>
       <c r="G8">
-        <v>-11.70177996620589</v>
+        <v>-14.53755108979429</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.59522857887657</v>
       </c>
       <c r="E9">
-        <v>-14.87771019881356</v>
+        <v>-19.57387812746196</v>
       </c>
       <c r="F9">
-        <v>-4.654594098475721</v>
+        <v>-5.114598942761329</v>
       </c>
       <c r="G9">
-        <v>-11.55949307450213</v>
+        <v>-12.88979216890468</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.34984639159884</v>
       </c>
       <c r="E10">
-        <v>-15.06328706364789</v>
+        <v>-20.45182696875103</v>
       </c>
       <c r="F10">
-        <v>-4.198399744242992</v>
+        <v>-4.832862077027786</v>
       </c>
       <c r="G10">
-        <v>-11.98770233167435</v>
+        <v>-13.09092448805553</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.06866804291568</v>
       </c>
       <c r="E11">
-        <v>-16.25268170481449</v>
+        <v>-19.9500403493831</v>
       </c>
       <c r="F11">
-        <v>-4.37931104317739</v>
+        <v>-4.843712033269654</v>
       </c>
       <c r="G11">
-        <v>-11.10824636076106</v>
+        <v>-12.69997350169081</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.755402347286878</v>
       </c>
       <c r="E12">
-        <v>-16.99404724155822</v>
+        <v>-20.38087936647286</v>
       </c>
       <c r="F12">
-        <v>-4.191400868056738</v>
+        <v>-5.164699431650046</v>
       </c>
       <c r="G12">
-        <v>-11.25097293615378</v>
+        <v>-12.76394419721374</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.420808502400648</v>
       </c>
       <c r="E13">
-        <v>-17.02879875109308</v>
+        <v>-20.93483853488316</v>
       </c>
       <c r="F13">
-        <v>-4.092004235027423</v>
+        <v>-4.300919322380861</v>
       </c>
       <c r="G13">
-        <v>-10.86739157341158</v>
+        <v>-11.93869072524092</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.096052193645784</v>
       </c>
       <c r="E14">
-        <v>-18.03676008114238</v>
+        <v>-22.56851723246829</v>
       </c>
       <c r="F14">
-        <v>-3.832094850357648</v>
+        <v>-3.701310548068856</v>
       </c>
       <c r="G14">
-        <v>-10.01657082304756</v>
+        <v>-11.73521561389663</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.806734300593343</v>
       </c>
       <c r="E15">
-        <v>-19.62848699552045</v>
+        <v>-22.80646589920133</v>
       </c>
       <c r="F15">
-        <v>-3.39185899413985</v>
+        <v>-3.691927630497346</v>
       </c>
       <c r="G15">
-        <v>-9.796909445750535</v>
+        <v>-12.08208995105333</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.581420663366233</v>
       </c>
       <c r="E16">
-        <v>-20.08617080652768</v>
+        <v>-24.05466730383154</v>
       </c>
       <c r="F16">
-        <v>-3.293853189979835</v>
+        <v>-3.781943002689957</v>
       </c>
       <c r="G16">
-        <v>-10.11131937679809</v>
+        <v>-11.25948114365742</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.435676836031538</v>
       </c>
       <c r="E17">
-        <v>-21.54546249855144</v>
+        <v>-24.92071078695446</v>
       </c>
       <c r="F17">
-        <v>-2.996171908477208</v>
+        <v>-3.643165783331553</v>
       </c>
       <c r="G17">
-        <v>-9.290105088564943</v>
+        <v>-11.76108148344974</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.3767379355956</v>
       </c>
       <c r="E18">
-        <v>-22.21664574512429</v>
+        <v>-25.81326848539227</v>
       </c>
       <c r="F18">
-        <v>-2.761340518559784</v>
+        <v>-4.006881200715746</v>
       </c>
       <c r="G18">
-        <v>-8.932524125459777</v>
+        <v>-11.1792716826368</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.401960263701666</v>
       </c>
       <c r="E19">
-        <v>-22.79437034512684</v>
+        <v>-27.7751392797353</v>
       </c>
       <c r="F19">
-        <v>-2.315012848461799</v>
+        <v>-3.506309547980241</v>
       </c>
       <c r="G19">
-        <v>-9.510432553838536</v>
+        <v>-11.58090632639907</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.493977131760685</v>
       </c>
       <c r="E20">
-        <v>-23.2804069318961</v>
+        <v>-26.68403516690518</v>
       </c>
       <c r="F20">
-        <v>-2.14334198790563</v>
+        <v>-3.229275323992391</v>
       </c>
       <c r="G20">
-        <v>-9.733818117605532</v>
+        <v>-11.45360805477885</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.634399004253954</v>
       </c>
       <c r="E21">
-        <v>-23.71784393561503</v>
+        <v>-27.42200434814316</v>
       </c>
       <c r="F21">
-        <v>-1.652164849885274</v>
+        <v>-2.619463548380105</v>
       </c>
       <c r="G21">
-        <v>-9.184863188267313</v>
+        <v>-11.44850903647547</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.79693783378252</v>
       </c>
       <c r="E22">
-        <v>-23.50591135205606</v>
+        <v>-27.98491178119261</v>
       </c>
       <c r="F22">
-        <v>-1.451574854929971</v>
+        <v>-2.204385210185328</v>
       </c>
       <c r="G22">
-        <v>-9.659600167152453</v>
+        <v>-11.25127152731569</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.958171214591413</v>
       </c>
       <c r="E23">
-        <v>-25.58577153666894</v>
+        <v>-29.93629010125987</v>
       </c>
       <c r="F23">
-        <v>-1.458805673989008</v>
+        <v>-2.142079555983763</v>
       </c>
       <c r="G23">
-        <v>-9.489751014349356</v>
+        <v>-11.11106493008062</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.095621427196001</v>
       </c>
       <c r="E24">
-        <v>-24.68738569218324</v>
+        <v>-29.28909418150565</v>
       </c>
       <c r="F24">
-        <v>-1.454832823925182</v>
+        <v>-1.815221517819732</v>
       </c>
       <c r="G24">
-        <v>-10.58822524313402</v>
+        <v>-11.32169966686761</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.185722372768041</v>
       </c>
       <c r="E25">
-        <v>-24.75386821908985</v>
+        <v>-30.14699999683678</v>
       </c>
       <c r="F25">
-        <v>-1.425052187427136</v>
+        <v>-2.268197664692585</v>
       </c>
       <c r="G25">
-        <v>-9.822237194967888</v>
+        <v>-11.81930019757896</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.215087507747858</v>
       </c>
       <c r="E26">
-        <v>-25.84758073294839</v>
+        <v>-30.87731152852778</v>
       </c>
       <c r="F26">
-        <v>-1.482870575407736</v>
+        <v>-2.049920368952707</v>
       </c>
       <c r="G26">
-        <v>-9.849198992521847</v>
+        <v>-11.61362338656829</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.167961337728345</v>
       </c>
       <c r="E27">
-        <v>-25.80784337353109</v>
+        <v>-30.29846386697132</v>
       </c>
       <c r="F27">
-        <v>-1.424293402886172</v>
+        <v>-2.25301369019927</v>
       </c>
       <c r="G27">
-        <v>-10.29159953293866</v>
+        <v>-12.31168030478924</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.039717310968685</v>
       </c>
       <c r="E28">
-        <v>-25.57396580493094</v>
+        <v>-30.07710752900239</v>
       </c>
       <c r="F28">
-        <v>-1.648764401696782</v>
+        <v>-2.387092409648996</v>
       </c>
       <c r="G28">
-        <v>-9.433435408724607</v>
+        <v>-11.85077695599872</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.831110000060953</v>
       </c>
       <c r="E29">
-        <v>-25.29348571031786</v>
+        <v>-30.09979065530681</v>
       </c>
       <c r="F29">
-        <v>-1.816854229970649</v>
+        <v>-2.093268835141205</v>
       </c>
       <c r="G29">
-        <v>-10.03179569108338</v>
+        <v>-11.99195151359383</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.549041050711603</v>
       </c>
       <c r="E30">
-        <v>-25.10901832161541</v>
+        <v>-28.33202384235456</v>
       </c>
       <c r="F30">
-        <v>-1.897522304390071</v>
+        <v>-1.883956959801826</v>
       </c>
       <c r="G30">
-        <v>-9.344671803098509</v>
+        <v>-11.81731177731394</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.210456761473194</v>
       </c>
       <c r="E31">
-        <v>-24.46107067517591</v>
+        <v>-30.32150247848535</v>
       </c>
       <c r="F31">
-        <v>-1.865294670584156</v>
+        <v>-2.60518829292766</v>
       </c>
       <c r="G31">
-        <v>-9.545029753961321</v>
+        <v>-11.97972240084178</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.831410902032498</v>
       </c>
       <c r="E32">
-        <v>-24.84486790427399</v>
+        <v>-30.47427507760812</v>
       </c>
       <c r="F32">
-        <v>-1.925053095022113</v>
+        <v>-2.548870078313531</v>
       </c>
       <c r="G32">
-        <v>-9.582386461415599</v>
+        <v>-11.19559247867348</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.436189497845075</v>
       </c>
       <c r="E33">
-        <v>-24.70481578863877</v>
+        <v>-30.82263246912217</v>
       </c>
       <c r="F33">
-        <v>-2.022379637911832</v>
+        <v>-2.502003535765343</v>
       </c>
       <c r="G33">
-        <v>-8.903272035257327</v>
+        <v>-10.63640998173447</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.045699532105187</v>
       </c>
       <c r="E34">
-        <v>-24.81769706022797</v>
+        <v>-30.6892824950183</v>
       </c>
       <c r="F34">
-        <v>-1.949909087310514</v>
+        <v>-2.418127194394879</v>
       </c>
       <c r="G34">
-        <v>-8.810095186633776</v>
+        <v>-11.44609733862928</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.680694066166529</v>
       </c>
       <c r="E35">
-        <v>-25.03767674209857</v>
+        <v>-29.78374166160048</v>
       </c>
       <c r="F35">
-        <v>-1.938423773270699</v>
+        <v>-2.574671237808527</v>
       </c>
       <c r="G35">
-        <v>-9.149084748383128</v>
+        <v>-10.87928600156456</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.362131129705557</v>
       </c>
       <c r="E36">
-        <v>-24.73610301555776</v>
+        <v>-28.35949809415909</v>
       </c>
       <c r="F36">
-        <v>-1.908175937557475</v>
+        <v>-3.042896800199517</v>
       </c>
       <c r="G36">
-        <v>-9.010105328011287</v>
+        <v>-10.88886060607502</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.102217846737994</v>
       </c>
       <c r="E37">
-        <v>-23.98940746490701</v>
+        <v>-28.4217283839725</v>
       </c>
       <c r="F37">
-        <v>-2.207842815724613</v>
+        <v>-2.672069020294887</v>
       </c>
       <c r="G37">
-        <v>-8.296554481586641</v>
+        <v>-10.6758010465556</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.914902715166857</v>
       </c>
       <c r="E38">
-        <v>-23.2356610802263</v>
+        <v>-27.77646612261955</v>
       </c>
       <c r="F38">
-        <v>-2.3370573617851</v>
+        <v>-2.803386791191081</v>
       </c>
       <c r="G38">
-        <v>-8.275013262048887</v>
+        <v>-10.492124826101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.802003983133481</v>
       </c>
       <c r="E39">
-        <v>-23.28221379302516</v>
+        <v>-28.33962262173943</v>
       </c>
       <c r="F39">
-        <v>-2.110471540995142</v>
+        <v>-2.738115581687494</v>
       </c>
       <c r="G39">
-        <v>-8.008551821649501</v>
+        <v>-10.17789864346078</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.764736849931297</v>
       </c>
       <c r="E40">
-        <v>-22.71893955358108</v>
+        <v>-27.6111270081255</v>
       </c>
       <c r="F40">
-        <v>-2.222581956922625</v>
+        <v>-2.727838855688364</v>
       </c>
       <c r="G40">
-        <v>-8.426717259628255</v>
+        <v>-10.03599237345792</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.796733351212269</v>
       </c>
       <c r="E41">
-        <v>-22.72946825564891</v>
+        <v>-27.88298488822797</v>
       </c>
       <c r="F41">
-        <v>-2.189651039191733</v>
+        <v>-2.927978218776544</v>
       </c>
       <c r="G41">
-        <v>-8.146025161325555</v>
+        <v>-10.42443650655122</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.889339753775373</v>
       </c>
       <c r="E42">
-        <v>-22.69514695114478</v>
+        <v>-27.50532826988429</v>
       </c>
       <c r="F42">
-        <v>-2.353318213902054</v>
+        <v>-2.8827816649124</v>
       </c>
       <c r="G42">
-        <v>-7.875993751869494</v>
+        <v>-9.89095581808734</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.033518482478677</v>
       </c>
       <c r="E43">
-        <v>-22.37514233539275</v>
+        <v>-27.73377166967524</v>
       </c>
       <c r="F43">
-        <v>-2.533385406452999</v>
+        <v>-3.220343866655407</v>
       </c>
       <c r="G43">
-        <v>-7.136104539987186</v>
+        <v>-10.12067085824251</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.216098856386792</v>
       </c>
       <c r="E44">
-        <v>-22.10247385844291</v>
+        <v>-24.82491544779619</v>
       </c>
       <c r="F44">
-        <v>-2.80675658978567</v>
+        <v>-3.011666520746572</v>
       </c>
       <c r="G44">
-        <v>-7.902952268201892</v>
+        <v>-9.838019870668818</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.426942104453592</v>
       </c>
       <c r="E45">
-        <v>-21.12818173264064</v>
+        <v>-27.09781089393404</v>
       </c>
       <c r="F45">
-        <v>-2.749991056774028</v>
+        <v>-3.061460513696253</v>
       </c>
       <c r="G45">
-        <v>-7.727511913861502</v>
+        <v>-9.553245932746171</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.650309764164933</v>
       </c>
       <c r="E46">
-        <v>-21.44691384719652</v>
+        <v>-25.47623680737141</v>
       </c>
       <c r="F46">
-        <v>-2.858334886120981</v>
+        <v>-3.713679730127458</v>
       </c>
       <c r="G46">
-        <v>-7.844717147964867</v>
+        <v>-10.01624598211318</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.877003680048222</v>
       </c>
       <c r="E47">
-        <v>-20.84365771073871</v>
+        <v>-25.42283251339895</v>
       </c>
       <c r="F47">
-        <v>-2.819660068819078</v>
+        <v>-3.653891484463001</v>
       </c>
       <c r="G47">
-        <v>-7.42922918677862</v>
+        <v>-9.855964871377422</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.09638949397724</v>
       </c>
       <c r="E48">
-        <v>-19.82034938227743</v>
+        <v>-24.30660442677427</v>
       </c>
       <c r="F48">
-        <v>-2.882403929376724</v>
+        <v>-3.208619982803586</v>
       </c>
       <c r="G48">
-        <v>-7.760868812234817</v>
+        <v>-10.15061856741556</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.302631027952764</v>
       </c>
       <c r="E49">
-        <v>-20.51720454799977</v>
+        <v>-26.11862348772949</v>
       </c>
       <c r="F49">
-        <v>-3.102468841971843</v>
+        <v>-3.245499727943622</v>
       </c>
       <c r="G49">
-        <v>-8.507786400697455</v>
+        <v>-9.9195516639779</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.495511485252824</v>
       </c>
       <c r="E50">
-        <v>-19.59987609673999</v>
+        <v>-23.37651926423489</v>
       </c>
       <c r="F50">
-        <v>-3.067452923488105</v>
+        <v>-3.557595430622364</v>
       </c>
       <c r="G50">
-        <v>-7.816931763799489</v>
+        <v>-9.976763043088379</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.675518071301605</v>
       </c>
       <c r="E51">
-        <v>-19.10040805606399</v>
+        <v>-25.12525290093291</v>
       </c>
       <c r="F51">
-        <v>-3.017075759886853</v>
+        <v>-3.73016175634096</v>
       </c>
       <c r="G51">
-        <v>-8.074891559138354</v>
+        <v>-10.12798141987695</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.850851884752297</v>
       </c>
       <c r="E52">
-        <v>-19.18724154516107</v>
+        <v>-23.93185961721753</v>
       </c>
       <c r="F52">
-        <v>-3.230438351825922</v>
+        <v>-3.109032825271626</v>
       </c>
       <c r="G52">
-        <v>-7.539793228445669</v>
+        <v>-9.260367377571695</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.02430406829305</v>
       </c>
       <c r="E53">
-        <v>-18.28850700817679</v>
+        <v>-22.69710325191609</v>
       </c>
       <c r="F53">
-        <v>-3.015351098954225</v>
+        <v>-3.22157564898337</v>
       </c>
       <c r="G53">
-        <v>-8.090004865641157</v>
+        <v>-10.41373972426743</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.203716516494017</v>
       </c>
       <c r="E54">
-        <v>-18.88054158604358</v>
+        <v>-22.86270501790259</v>
       </c>
       <c r="F54">
-        <v>-3.027474255894195</v>
+        <v>-3.934327813374149</v>
       </c>
       <c r="G54">
-        <v>-7.921940697366399</v>
+        <v>-9.849123524425979</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.39195925781593</v>
       </c>
       <c r="E55">
-        <v>-18.15462720261402</v>
+        <v>-21.41588021482195</v>
       </c>
       <c r="F55">
-        <v>-3.294242522659151</v>
+        <v>-3.583513389921155</v>
       </c>
       <c r="G55">
-        <v>-7.810211822045746</v>
+        <v>-10.53437711612197</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.587992869414908</v>
       </c>
       <c r="E56">
-        <v>-17.91207760628919</v>
+        <v>-22.49434535669666</v>
       </c>
       <c r="F56">
-        <v>-3.086880624185962</v>
+        <v>-3.600385577181375</v>
       </c>
       <c r="G56">
-        <v>-7.694719385596411</v>
+        <v>-9.830181032363305</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.791286366280495</v>
       </c>
       <c r="E57">
-        <v>-17.51910568885157</v>
+        <v>-21.56812298248582</v>
       </c>
       <c r="F57">
-        <v>-3.180359400489678</v>
+        <v>-3.614479420172606</v>
       </c>
       <c r="G57">
-        <v>-8.687429999855494</v>
+        <v>-10.19048540936281</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.994011293624531</v>
       </c>
       <c r="E58">
-        <v>-17.217083643384</v>
+        <v>-21.71268092975867</v>
       </c>
       <c r="F58">
-        <v>-3.039739063660045</v>
+        <v>-3.38894728271901</v>
       </c>
       <c r="G58">
-        <v>-8.650919847563552</v>
+        <v>-10.44864864043836</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.195530049735371</v>
       </c>
       <c r="E59">
-        <v>-15.58193772022038</v>
+        <v>-20.24500703234672</v>
       </c>
       <c r="F59">
-        <v>-3.187553771382992</v>
+        <v>-3.700635428635574</v>
       </c>
       <c r="G59">
-        <v>-8.618567002987428</v>
+        <v>-11.09466866594807</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.390588494440296</v>
       </c>
       <c r="E60">
-        <v>-16.6666068714856</v>
+        <v>-20.19099592285723</v>
       </c>
       <c r="F60">
-        <v>-2.949389859404106</v>
+        <v>-3.442279232846048</v>
       </c>
       <c r="G60">
-        <v>-8.03112662597848</v>
+        <v>-11.2524199548615</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.576577224566197</v>
       </c>
       <c r="E61">
-        <v>-15.85446128600198</v>
+        <v>-19.8257020385545</v>
       </c>
       <c r="F61">
-        <v>-3.104381542304907</v>
+        <v>-3.741926230195519</v>
       </c>
       <c r="G61">
-        <v>-8.310388111681261</v>
+        <v>-10.71787615061236</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.753928184874136</v>
       </c>
       <c r="E62">
-        <v>-15.49693826309641</v>
+        <v>-20.22921171500796</v>
       </c>
       <c r="F62">
-        <v>-3.237771060075503</v>
+        <v>-3.6519381941272</v>
       </c>
       <c r="G62">
-        <v>-8.725928572412458</v>
+        <v>-11.31190522051267</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.918923142263612</v>
       </c>
       <c r="E63">
-        <v>-15.85990904023321</v>
+        <v>-19.75513029961896</v>
       </c>
       <c r="F63">
-        <v>-3.314731361999994</v>
+        <v>-3.478704204281947</v>
       </c>
       <c r="G63">
-        <v>-8.894550548352322</v>
+        <v>-10.82994955419675</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.07354479883501</v>
       </c>
       <c r="E64">
-        <v>-16.28609731451709</v>
+        <v>-20.93245202908112</v>
       </c>
       <c r="F64">
-        <v>-3.338228831747805</v>
+        <v>-3.612234544511019</v>
       </c>
       <c r="G64">
-        <v>-9.124554336004719</v>
+        <v>-10.99664545308122</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.21430884694773</v>
       </c>
       <c r="E65">
-        <v>-15.594703488448</v>
+        <v>-19.62762205698499</v>
       </c>
       <c r="F65">
-        <v>-3.511233363822481</v>
+        <v>-3.466899140424652</v>
       </c>
       <c r="G65">
-        <v>-8.494750107441781</v>
+        <v>-11.87769281645084</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.34328299836537</v>
       </c>
       <c r="E66">
-        <v>-14.98102280482455</v>
+        <v>-19.24181871390151</v>
       </c>
       <c r="F66">
-        <v>-3.409120514079386</v>
+        <v>-3.651641638596998</v>
       </c>
       <c r="G66">
-        <v>-8.985670071058102</v>
+        <v>-11.57300186366237</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.4632011197376</v>
       </c>
       <c r="E67">
-        <v>-16.18952307782951</v>
+        <v>-20.11872600616882</v>
       </c>
       <c r="F67">
-        <v>-3.187141244416397</v>
+        <v>-3.215888906763151</v>
       </c>
       <c r="G67">
-        <v>-9.783433468805896</v>
+        <v>-12.02775620325049</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.57423848513267</v>
       </c>
       <c r="E68">
-        <v>-15.55440912672775</v>
+        <v>-19.37195799993394</v>
       </c>
       <c r="F68">
-        <v>-3.624423142475811</v>
+        <v>-3.569859410020811</v>
       </c>
       <c r="G68">
-        <v>-9.069095129206984</v>
+        <v>-11.76479254503347</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.68149307136976</v>
       </c>
       <c r="E69">
-        <v>-15.2323214129322</v>
+        <v>-19.92037431615885</v>
       </c>
       <c r="F69">
-        <v>-3.473471407398463</v>
+        <v>-3.451841077776562</v>
       </c>
       <c r="G69">
-        <v>-9.249332629467283</v>
+        <v>-11.3212960766158</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.78308564071698</v>
       </c>
       <c r="E70">
-        <v>-15.13165796421569</v>
+        <v>-19.05399572595937</v>
       </c>
       <c r="F70">
-        <v>-3.24615579492664</v>
+        <v>-3.784134862837765</v>
       </c>
       <c r="G70">
-        <v>-9.383669121332508</v>
+        <v>-10.97786702209652</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.88393719098127</v>
       </c>
       <c r="E71">
-        <v>-15.59029728323854</v>
+        <v>-19.49940284393181</v>
       </c>
       <c r="F71">
-        <v>-3.626568614049062</v>
+        <v>-3.491504137390006</v>
       </c>
       <c r="G71">
-        <v>-8.605894925324852</v>
+        <v>-11.73580623377733</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.98382692532917</v>
       </c>
       <c r="E72">
-        <v>-15.06876651719717</v>
+        <v>-20.0465104311685</v>
       </c>
       <c r="F72">
-        <v>-3.51408543279032</v>
+        <v>-3.364523698214869</v>
       </c>
       <c r="G72">
-        <v>-9.553918583165856</v>
+        <v>-11.97479728728105</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.08023482633883</v>
       </c>
       <c r="E73">
-        <v>-15.47256148751312</v>
+        <v>-19.01134655775514</v>
       </c>
       <c r="F73">
-        <v>-3.452508741903219</v>
+        <v>-3.670400846800795</v>
       </c>
       <c r="G73">
-        <v>-8.882147530857621</v>
+        <v>-11.00569834336373</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.17289191743715</v>
       </c>
       <c r="E74">
-        <v>-15.51224903371634</v>
+        <v>-19.85057241780462</v>
       </c>
       <c r="F74">
-        <v>-3.523875078756605</v>
+        <v>-3.850212902191678</v>
       </c>
       <c r="G74">
-        <v>-8.428364432851096</v>
+        <v>-11.6049576804298</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.25487588920164</v>
       </c>
       <c r="E75">
-        <v>-15.319580578586</v>
+        <v>-20.73868768324092</v>
       </c>
       <c r="F75">
-        <v>-3.693726016128823</v>
+        <v>-3.713456070928702</v>
       </c>
       <c r="G75">
-        <v>-8.996038731185948</v>
+        <v>-10.69347370587477</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.32462748115442</v>
       </c>
       <c r="E76">
-        <v>-15.58156638535175</v>
+        <v>-20.59894350383822</v>
       </c>
       <c r="F76">
-        <v>-3.768081930938913</v>
+        <v>-3.653061460325396</v>
       </c>
       <c r="G76">
-        <v>-8.651841870821757</v>
+        <v>-11.14577697295799</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.3758826762654</v>
       </c>
       <c r="E77">
-        <v>-16.01353299246942</v>
+        <v>-19.71013991035275</v>
       </c>
       <c r="F77">
-        <v>-3.635699707930121</v>
+        <v>-3.885903940108698</v>
       </c>
       <c r="G77">
-        <v>-7.953653703738431</v>
+        <v>-10.63216079981498</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.40504465334952</v>
       </c>
       <c r="E78">
-        <v>-16.42541581736307</v>
+        <v>-20.82376865289703</v>
       </c>
       <c r="F78">
-        <v>-3.652940518684587</v>
+        <v>-4.31564272459822</v>
       </c>
       <c r="G78">
-        <v>-8.492935591919409</v>
+        <v>-9.598726944781633</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.41352469226974</v>
       </c>
       <c r="E79">
-        <v>-17.13634095182724</v>
+        <v>-20.66099718316532</v>
       </c>
       <c r="F79">
-        <v>-3.606543660453787</v>
+        <v>-4.157552119243546</v>
       </c>
       <c r="G79">
-        <v>-8.707609512446078</v>
+        <v>-9.208671731902644</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.39966658290835</v>
       </c>
       <c r="E80">
-        <v>-16.9930917335426</v>
+        <v>-22.84738971880865</v>
       </c>
       <c r="F80">
-        <v>-4.097714999902323</v>
+        <v>-4.070796372780951</v>
       </c>
       <c r="G80">
-        <v>-8.133983078202395</v>
+        <v>-9.880213098701718</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.36944997802916</v>
       </c>
       <c r="E81">
-        <v>-18.22325169772625</v>
+        <v>-22.54527710386093</v>
       </c>
       <c r="F81">
-        <v>-3.938872236945906</v>
+        <v>-3.973391134987965</v>
       </c>
       <c r="G81">
-        <v>-8.012456475305241</v>
+        <v>-10.32693828913388</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.32362174500249</v>
       </c>
       <c r="E82">
-        <v>-18.62374993896462</v>
+        <v>-22.92913320312111</v>
       </c>
       <c r="F82">
-        <v>-4.241107054061723</v>
+        <v>-4.899872858077252</v>
       </c>
       <c r="G82">
-        <v>-7.53754559167745</v>
+        <v>-9.34784802556805</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.27025052244058</v>
       </c>
       <c r="E83">
-        <v>-19.30113719492799</v>
+        <v>-23.79145428060971</v>
       </c>
       <c r="F83">
-        <v>-4.140126582558254</v>
+        <v>-4.610790030215684</v>
       </c>
       <c r="G83">
-        <v>-8.344588283995353</v>
+        <v>-10.77807016012037</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.2149957576555</v>
       </c>
       <c r="E84">
-        <v>-19.32902353786722</v>
+        <v>-24.3295230337271</v>
       </c>
       <c r="F84">
-        <v>-4.271097267512676</v>
+        <v>-4.3065232278608</v>
       </c>
       <c r="G84">
-        <v>-7.854659249289984</v>
+        <v>-9.929428140871829</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.16055054193781</v>
       </c>
       <c r="E85">
-        <v>-20.59119528481109</v>
+        <v>-25.55976451044289</v>
       </c>
       <c r="F85">
-        <v>-4.431783147940322</v>
+        <v>-4.4551232278816</v>
       </c>
       <c r="G85">
-        <v>-7.811858995268588</v>
+        <v>-10.70315330947513</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.11562146113827</v>
       </c>
       <c r="E86">
-        <v>-21.86653130569526</v>
+        <v>-25.82779583000888</v>
       </c>
       <c r="F86">
-        <v>-4.528361675065313</v>
+        <v>-4.798443411441466</v>
       </c>
       <c r="G86">
-        <v>-8.046564773415668</v>
+        <v>-9.847666662053586</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.08343105144202</v>
       </c>
       <c r="E87">
-        <v>-23.01717126630423</v>
+        <v>-27.65649326073434</v>
       </c>
       <c r="F87">
-        <v>-4.470118334607077</v>
+        <v>-4.981559824402117</v>
       </c>
       <c r="G87">
-        <v>-8.246889912062887</v>
+        <v>-9.78470658277096</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.07515080166074</v>
       </c>
       <c r="E88">
-        <v>-24.58500595181783</v>
+        <v>-28.37313332939619</v>
       </c>
       <c r="F88">
-        <v>-4.718298865220614</v>
+        <v>-4.712884655875917</v>
       </c>
       <c r="G88">
-        <v>-8.466177230102137</v>
+        <v>-10.34243549855914</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.09640997679187</v>
       </c>
       <c r="E89">
-        <v>-25.7026469223329</v>
+        <v>-28.79723397716253</v>
       </c>
       <c r="F89">
-        <v>-4.576005226237327</v>
+        <v>-4.739147216014272</v>
       </c>
       <c r="G89">
-        <v>-8.350924322826641</v>
+        <v>-10.98792396617622</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.1545666920059</v>
       </c>
       <c r="E90">
-        <v>-26.93914675012729</v>
+        <v>-31.64887519419166</v>
       </c>
       <c r="F90">
-        <v>-4.399560484338823</v>
+        <v>-5.062505401901476</v>
       </c>
       <c r="G90">
-        <v>-8.664786289873765</v>
+        <v>-9.663724662652674</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.2595111643976</v>
       </c>
       <c r="E91">
-        <v>-29.20161312062547</v>
+        <v>-32.62253106939585</v>
       </c>
       <c r="F91">
-        <v>-4.612214822148498</v>
+        <v>-5.167148085692721</v>
       </c>
       <c r="G91">
-        <v>-8.597052033222148</v>
+        <v>-10.22104998818904</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.41413500073114</v>
       </c>
       <c r="E92">
-        <v>-31.15092645654523</v>
+        <v>-34.58853636050787</v>
       </c>
       <c r="F92">
-        <v>-4.759262461656453</v>
+        <v>-4.987978843406411</v>
       </c>
       <c r="G92">
-        <v>-9.264098126484784</v>
+        <v>-10.6500237699846</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.62627347269395</v>
       </c>
       <c r="E93">
-        <v>-32.76523460656256</v>
+        <v>-36.15353169281867</v>
       </c>
       <c r="F93">
-        <v>-4.72090159560021</v>
+        <v>-5.391736712674529</v>
       </c>
       <c r="G93">
-        <v>-9.467999796631798</v>
+        <v>-11.08663951679211</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.8900608030115</v>
       </c>
       <c r="E94">
-        <v>-33.97268653783475</v>
+        <v>-37.60317547096909</v>
       </c>
       <c r="F94">
-        <v>-4.419992166328873</v>
+        <v>-4.725255494669325</v>
       </c>
       <c r="G94">
-        <v>-9.408055159962302</v>
+        <v>-11.68750008997919</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.20723845919659</v>
       </c>
       <c r="E95">
-        <v>-37.15335761931318</v>
+        <v>-39.85248888871199</v>
       </c>
       <c r="F95">
-        <v>-4.515567540529075</v>
+        <v>-5.176391837540561</v>
       </c>
       <c r="G95">
-        <v>-10.13046530459745</v>
+        <v>-11.30407622587184</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.57555383789712</v>
       </c>
       <c r="E96">
-        <v>-39.4197999899901</v>
+        <v>-43.17272980334383</v>
       </c>
       <c r="F96">
-        <v>-4.248407455982595</v>
+        <v>-5.516899713767923</v>
       </c>
       <c r="G96">
-        <v>-10.76517824061331</v>
+        <v>-11.82731294062713</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.98262733720378</v>
       </c>
       <c r="E97">
-        <v>-41.5911240283729</v>
+        <v>-44.79362009033131</v>
       </c>
       <c r="F97">
-        <v>-4.455042876243529</v>
+        <v>-4.799535199678356</v>
       </c>
       <c r="G97">
-        <v>-10.22482011176084</v>
+        <v>-12.35110090060441</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.43446387958578</v>
       </c>
       <c r="E98">
-        <v>-44.16551395275642</v>
+        <v>-46.80861894173233</v>
       </c>
       <c r="F98">
-        <v>-4.423086946945732</v>
+        <v>-4.890644845210065</v>
       </c>
       <c r="G98">
-        <v>-10.9166623963482</v>
+        <v>-12.52421486885915</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.9024331310986</v>
       </c>
       <c r="E99">
-        <v>-45.99629221728841</v>
+        <v>-49.82516114339526</v>
       </c>
       <c r="F99">
-        <v>-4.177099933214808</v>
+        <v>-5.231644771674691</v>
       </c>
       <c r="G99">
-        <v>-10.76015797162736</v>
+        <v>-12.58353607343235</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.40667141633861</v>
       </c>
       <c r="E100">
-        <v>-48.13681583970804</v>
+        <v>-51.48554312008513</v>
       </c>
       <c r="F100">
-        <v>-3.978402757774902</v>
+        <v>-4.588210391550175</v>
       </c>
       <c r="G100">
-        <v>-11.16444384240967</v>
+        <v>-12.37952284175232</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-14.89243614400015</v>
       </c>
       <c r="E101">
-        <v>-50.87910686275545</v>
+        <v>-54.46894934531544</v>
       </c>
       <c r="F101">
-        <v>-3.8501897079044</v>
+        <v>-4.516037224846462</v>
       </c>
       <c r="G101">
-        <v>-12.26049981090502</v>
+        <v>-13.27512570395963</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-15.41409494811511</v>
       </c>
       <c r="E102">
-        <v>-53.33108307776362</v>
+        <v>-54.99505047374906</v>
       </c>
       <c r="F102">
-        <v>-4.095802299569259</v>
+        <v>-5.061677862866079</v>
       </c>
       <c r="G102">
-        <v>-12.4355365749936</v>
+        <v>-14.22931149588928</v>
       </c>
     </row>
   </sheetData>
